--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:21</t>
+    <t xml:space="preserve">2026-09-10 01:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:35</t>
+    <t xml:space="preserve">2026-09-18 11:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:31</t>
+    <t xml:space="preserve">2026-09-23 15:36</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_e_matricula_a_2018_la_araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_e_matricula_a_2018_la_araucania.xlsx
@@ -150,7 +150,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 15:36</t>
+    <t xml:space="preserve">2026-10-05 16:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1260,7 +1260,7 @@
         <v>84.95</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>33.12</v>
+        <v>33.13</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>62.95</v>
